--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104741_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104741_W32.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0476</v>
+        <v>5.5949</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7556</v>
+        <v>1.5112</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2921</v>
+        <v>4.0837</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4909</v>
+        <v>3.4893</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8386</v>
+        <v>1.8355</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6524</v>
+        <v>1.6538</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9913</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4944</v>
+        <v>2.498</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9166</v>
+        <v>0.9187</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5778</v>
+        <v>1.5793</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4885</v>
+        <v>1.0374</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5996</v>
+        <v>0.3622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8889</v>
+        <v>0.6752</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2694</v>
+        <v>5.2408</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3846</v>
+        <v>3.433</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8848</v>
+        <v>1.8078</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0977</v>
+        <v>1.0964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3261</v>
+        <v>0.3247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7716</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5164</v>
+        <v>0.5077</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6342</v>
+        <v>0.627</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1178</v>
+        <v>-0.1194</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5813</v>
+        <v>0.5887</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3081</v>
+        <v>-0.3023</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8894</v>
+        <v>0.8911</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6242</v>
+        <v>-0.6491</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1105</v>
+        <v>-1.0455</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4863</v>
+        <v>0.3964</v>
       </c>
       <c r="V3" t="n">
-        <v>3.66</v>
+        <v>3.6554</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9788</v>
+        <v>3.9709</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3201</v>
+        <v>4.1762</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2673</v>
+        <v>0.9489</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0528</v>
+        <v>3.2272</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4903</v>
+        <v>-0.4998</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2066</v>
+        <v>-1.2113</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7163</v>
+        <v>0.7114</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2305</v>
+        <v>-1.2493</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3869</v>
+        <v>-1.3972</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1564</v>
+        <v>0.1478</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7402</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1803</v>
+        <v>0.1859</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5599</v>
+        <v>0.5636</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.508</v>
+        <v>0.3589</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2304</v>
+        <v>-0.5255</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.8843</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6346</v>
+        <v>2.563</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3707</v>
+        <v>0.3813</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0054</v>
+        <v>2.1817</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1182</v>
+        <v>0.2772</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2772</v>
+        <v>1.5047</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3954</v>
+        <v>-1.2275</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4151</v>
+        <v>0.1727</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2247</v>
+        <v>1.2755</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6398</v>
+        <v>-1.1029</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2969</v>
+        <v>0.1046</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0526</v>
+        <v>0.2292</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2443</v>
+        <v>-0.1246</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5491</v>
+        <v>1.0777</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0444</v>
+        <v>0.2086</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5048</v>
+        <v>0.8691</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.494</v>
+        <v>2.2554</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2984</v>
+        <v>0.7583</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1956</v>
+        <v>1.4971</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6421</v>
+        <v>0.6398</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2532</v>
+        <v>1.2522</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6112</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4053</v>
+        <v>0.393</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7342</v>
+        <v>1.7269</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3288</v>
+        <v>-1.334</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2368</v>
+        <v>0.2468</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7177</v>
+        <v>0.7215</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6482</v>
+        <v>0.4076</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3474</v>
+        <v>-0.1794</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3008</v>
+        <v>0.587</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9448</v>
+        <v>2.1797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1547</v>
+        <v>-0.3752</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7902</v>
+        <v>2.5549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2766</v>
+        <v>-0.112</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5042</v>
+        <v>0.2809</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2276</v>
+        <v>-0.393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1797</v>
+        <v>-0.4166</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2788</v>
+        <v>0.2241</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0991</v>
+        <v>-0.6407</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0969</v>
+        <v>0.3046</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2254</v>
+        <v>0.0568</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1285</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4645</v>
+        <v>1.0837</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.025</v>
+        <v>0.0414</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4896</v>
+        <v>1.0423</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7853</v>
+        <v>1.3583</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7442</v>
+        <v>0.1681</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5295</v>
+        <v>1.1902</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1107</v>
+        <v>2.1919</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5094</v>
+        <v>0.8218</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3988</v>
+        <v>1.3701</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.492</v>
+        <v>1.7454</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3742</v>
+        <v>0.4202</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1178</v>
+        <v>1.3252</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3813</v>
+        <v>0.4465</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1353</v>
+        <v>0.4016</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9194</v>
+        <v>0.4623</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2522</v>
+        <v>-0.3904</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1716</v>
+        <v>0.8528</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1594</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4394</v>
+        <v>1.1654</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0483</v>
+        <v>-1.0369</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4877</v>
+        <v>2.2023</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1984</v>
+        <v>-0.1066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.825</v>
+        <v>-0.5059</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3734</v>
+        <v>0.3993</v>
       </c>
       <c r="J9" t="n">
-        <v>1.757</v>
+        <v>-0.4953</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4268</v>
+        <v>-0.376</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3301</v>
+        <v>-0.1194</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4415</v>
+        <v>0.3887</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3982</v>
+        <v>-0.13</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0433</v>
+        <v>0.5187</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5363</v>
+        <v>0.2916</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6247</v>
+        <v>-0.5415</v>
       </c>
       <c r="U9" t="n">
-        <v>1.161</v>
+        <v>0.8331</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2507</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0487</v>
+        <v>-1.6806</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7607</v>
+        <v>-1.5918</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.288</v>
+        <v>-0.0888</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4478</v>
+        <v>0.4453</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6282</v>
+        <v>0.6238</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1804</v>
+        <v>-0.1785</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0253</v>
+        <v>1.0173</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8761</v>
+        <v>0.8683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5775</v>
+        <v>-0.572</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.248</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3609</v>
+        <v>0.0139</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8329</v>
+        <v>-0.6483</v>
       </c>
       <c r="U10" t="n">
-        <v>0.472</v>
+        <v>0.6622</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5726</v>
+        <v>-2.6532</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7822</v>
+        <v>-1.0292</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7904</v>
+        <v>-1.624</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3201</v>
+        <v>-0.3163</v>
       </c>
       <c r="H11" t="n">
-        <v>0.13</v>
+        <v>0.1318</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.45</v>
+        <v>-0.4482</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9186</v>
+        <v>0.9163</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8813</v>
+        <v>0.8791</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2387</v>
+        <v>-1.2326</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7514</v>
+        <v>-0.7472</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4873</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1166</v>
+        <v>-0.1988</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0254</v>
+        <v>-0.214</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.142</v>
+        <v>0.0152</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5451</v>
+        <v>-3.0805</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1288</v>
+        <v>-0.9605</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4163</v>
+        <v>-2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0721</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6958</v>
+        <v>1.692</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7616</v>
+        <v>-1.7642</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0038</v>
+        <v>-0.016</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9588</v>
+        <v>1.951</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9626</v>
+        <v>-1.967</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0619</v>
+        <v>-0.0562</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.263</v>
+        <v>-0.259</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6834</v>
+        <v>-0.2148</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5089</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0107</v>
+        <v>0.294</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.5687</v>
+        <v>-2.5659</v>
       </c>
       <c r="W12" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.7688</v>
+        <v>17.1194</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0257</v>
+        <v>2.2072</v>
       </c>
       <c r="F13" t="n">
-        <v>14.7434</v>
+        <v>14.9121</v>
       </c>
       <c r="G13" t="n">
-        <v>7.0485</v>
+        <v>7.0331</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7623</v>
+        <v>6.7502</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2862999999999998</v>
+        <v>0.2825</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6574</v>
+        <v>3.5665</v>
       </c>
       <c r="K13" t="n">
-        <v>7.175700000000001</v>
+        <v>7.1157</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.5184</v>
+        <v>-3.5498</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3912</v>
+        <v>3.466600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4136</v>
+        <v>-0.3656000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>3.804799999999999</v>
+        <v>3.8321</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5436</v>
+        <v>4.5527</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.951599999999999</v>
+        <v>-7.9671</v>
       </c>
       <c r="R13" t="n">
-        <v>12.495</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3129</v>
+        <v>3.6704</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.753</v>
+        <v>-3.4413</v>
       </c>
       <c r="U13" t="n">
-        <v>7.066</v>
+        <v>7.1116</v>
       </c>
       <c r="V13" t="n">
-        <v>1.863799999999999</v>
+        <v>1.8634</v>
       </c>
       <c r="W13" t="n">
-        <v>10.0726</v>
+        <v>10.0493</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.209099999999999</v>
+        <v>-8.186</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0062</v>
+        <v>2.9924</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9206</v>
+        <v>-1.0517</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9269</v>
+        <v>4.044</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3547</v>
+        <v>1.3588</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6837</v>
+        <v>0.6886</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="J14" t="n">
-        <v>0.114</v>
+        <v>0.1079</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6913</v>
+        <v>0.6895</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5772</v>
+        <v>-0.5816</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2407</v>
+        <v>1.2509</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0076</v>
+        <v>-0.0009</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2483</v>
+        <v>1.2518</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4247</v>
+        <v>0.4043</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8075</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2322</v>
+        <v>1.3363</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6624</v>
+        <v>2.855</v>
       </c>
       <c r="E15" t="n">
-        <v>1.191</v>
+        <v>0.9319</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4714</v>
+        <v>1.9231</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0415</v>
+        <v>2.0375</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9197</v>
+        <v>0.914</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1218</v>
+        <v>1.1235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1678</v>
+        <v>0.1564</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8822</v>
+        <v>0.8716</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8736</v>
+        <v>1.881</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0375</v>
+        <v>0.0424</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8361</v>
+        <v>1.8386</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1754</v>
+        <v>0.0256</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1828</v>
+        <v>-0.4231</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0074</v>
+        <v>0.4487</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3919</v>
+        <v>0.6371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5206</v>
+        <v>-0.3558</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1286</v>
+        <v>0.9929</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6775</v>
+        <v>2.7904</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7965</v>
+        <v>0.5921</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4739</v>
+        <v>2.1983</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6758</v>
+        <v>2.8013</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3456</v>
+        <v>1.2681</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3301</v>
+        <v>1.5333</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9983</v>
+        <v>-0.0109</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1421</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1438</v>
+        <v>0.665</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4544</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6816</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.763</v>
+        <v>-0.1533</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1105</v>
+        <v>-0.6532</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3475</v>
+        <v>0.4999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9318</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2933</v>
+        <v>0.536</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2074</v>
+        <v>0.7429</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5007</v>
+        <v>-0.2068</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7981</v>
+        <v>0.681</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5958</v>
+        <v>-0.7906</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2023</v>
+        <v>1.4715</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8215</v>
+        <v>1.6699</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2796</v>
+        <v>0.3447</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5418</v>
+        <v>1.3252</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0234</v>
+        <v>-0.989</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6838</v>
+        <v>-1.1353</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6604</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9087</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4991</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5903</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5048</v>
+        <v>-0.6214</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5298</v>
+        <v>-0.8784</v>
       </c>
       <c r="U17" t="n">
-        <v>0.025</v>
+        <v>0.257</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0913</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2944</v>
+        <v>-0.8119</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4398</v>
+        <v>-0.2186</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8546</v>
+        <v>-0.5934</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7238</v>
+        <v>-0.7212</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0045</v>
+        <v>0.0056</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.7268</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1843</v>
+        <v>0.1811</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8986</v>
+        <v>0.8963</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9081</v>
+        <v>-0.9023</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.014</v>
+        <v>-0.0116</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6853</v>
+        <v>-0.1998</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.4601</v>
       </c>
       <c r="U18" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.2603</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3419</v>
+        <v>2.3367</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3863</v>
+        <v>-1.478</v>
       </c>
       <c r="E19" t="n">
-        <v>1.233</v>
+        <v>1.2276</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6192</v>
+        <v>-2.7056</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2544</v>
+        <v>-1.2515</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3111</v>
+        <v>-0.3103</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9433</v>
+        <v>-0.9412</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6276</v>
+        <v>0.6261</v>
       </c>
       <c r="K19" t="n">
-        <v>0.553</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.882</v>
+        <v>-1.8775</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8641</v>
+        <v>-0.8618</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0179</v>
+        <v>-1.0157</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3591</v>
+        <v>-0.4542</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4858</v>
+        <v>-0.4879</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1268</v>
+        <v>0.0338</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8804</v>
+        <v>-2.3792</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0468</v>
+        <v>-1.523</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8336</v>
+        <v>-0.8562</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.625</v>
+        <v>-2.6231</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.39</v>
+        <v>-2.3894</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.235</v>
+        <v>-0.2337</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4887</v>
+        <v>-1.4903</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.526</v>
+        <v>-1.5276</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1363</v>
+        <v>-1.1328</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8641</v>
+        <v>-0.8618</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7681</v>
+        <v>0.2636</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4419</v>
+        <v>-0.0327</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3262</v>
+        <v>0.2962</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0448</v>
+        <v>-3.6872</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0351</v>
+        <v>-3.1902</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0097</v>
+        <v>-0.4969</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7732</v>
+        <v>-1.0794</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.3405</v>
+        <v>-1.4684</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4327</v>
+        <v>0.389</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3871</v>
+        <v>-0.9105</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.71</v>
+        <v>-1.4242</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6771</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3861</v>
+        <v>-0.1689</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6305</v>
+        <v>-0.0442</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2443</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4331</v>
+        <v>-0.9233</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3285</v>
+        <v>-1.3872</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1046</v>
+        <v>0.4639</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9318</v>
+        <v>-0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1594</v>
+        <v>0.4733</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1716</v>
+        <v>-4.5694</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5264</v>
+        <v>-3.6399</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6452</v>
+        <v>-0.9296</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0875</v>
+        <v>-3.7676</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4749</v>
+        <v>-3.3374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3875</v>
+        <v>-0.4302</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9063</v>
+        <v>-2.3919</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4223</v>
+        <v>-1.7139</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5159</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1811</v>
+        <v>-1.3758</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0527</v>
+        <v>-1.6235</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1285</v>
+        <v>0.2477</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9087</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4544</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4029</v>
+        <v>-0.0977</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7352</v>
+        <v>-0.2676</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3323</v>
+        <v>0.1699</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7724</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0.4782</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2507</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4693</v>
+        <v>-4.9332</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3916</v>
+        <v>-4.0539</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0776</v>
+        <v>-0.8792</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0319</v>
+        <v>-2.0331</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5147</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5172</v>
+        <v>-1.5164</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9209000000000001</v>
+        <v>-0.9295</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5824</v>
+        <v>0.5753</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5032</v>
+        <v>-1.5048</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.111</v>
+        <v>-1.1036</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.097</v>
+        <v>-1.092</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.014</v>
+        <v>-0.0116</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1656</v>
+        <v>-0.6238</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9717</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1939</v>
+        <v>-0.0033</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.876</v>
+        <v>-5.1428</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6656</v>
+        <v>-4.3261</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2104</v>
+        <v>-0.8167</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4244</v>
+        <v>-2.4247</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1383</v>
+        <v>-0.1379</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2861</v>
+        <v>-2.2868</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2791</v>
+        <v>-3.2872</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1659</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1183</v>
+        <v>-3.1213</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8547</v>
+        <v>0.8625</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0225</v>
+        <v>0.028</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8345</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8828</v>
+        <v>-0.1522</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3187</v>
+        <v>-0.969</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4359</v>
+        <v>0.8168</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5687</v>
+        <v>-2.5659</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.769</v>
+        <v>-15.9812</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.2887</v>
+        <v>-15.4568</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4799</v>
+        <v>-0.5244000000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.048399999999999</v>
+        <v>-7.0329</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.762300000000002</v>
+        <v>-6.750300000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2859999999999991</v>
+        <v>-0.2824999999999998</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.3911</v>
+        <v>-3.4667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4137000000000005</v>
+        <v>0.3655000000000002</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.8047</v>
+        <v>-3.832199999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.657299999999999</v>
+        <v>-3.566400000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.175999999999999</v>
+        <v>-7.115700000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>3.518400000000001</v>
+        <v>3.549399999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.5436</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4953</v>
+        <v>-12.5197</v>
       </c>
       <c r="R25" t="n">
-        <v>7.951699999999999</v>
+        <v>7.9671</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.313</v>
+        <v>-2.5322</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.065700000000001</v>
+        <v>-7.1117</v>
       </c>
       <c r="U25" t="n">
-        <v>3.752800000000001</v>
+        <v>4.5795</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8636</v>
+        <v>-1.8635</v>
       </c>
       <c r="W25" t="n">
-        <v>7.6634</v>
+        <v>7.641299999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.5273</v>
+        <v>-9.504799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104741_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104741_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.186</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104741_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.504799999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
